--- a/documents/Literature_Review_Matrix_Dropout_Prediction_Updated.xlsx
+++ b/documents/Literature_Review_Matrix_Dropout_Prediction_Updated.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4948ECF6-3B97-469B-B5E0-1A83847556EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Literature Review" state="visible" r:id="rId4"/>
+    <sheet name="Literature Review" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -226,23 +230,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -300,12 +313,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -646,24 +660,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="42.142857142857146" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="35" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="35" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="42.142857142857146" customWidth="1"/>
-    <col min="11" max="24" width="13.571428571428571" customWidth="1"/>
+    <col min="1" max="1" width="12" style="2" customWidth="1"/>
+    <col min="2" max="2" width="42.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30" style="2" customWidth="1"/>
+    <col min="7" max="7" width="40" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20" style="2" customWidth="1"/>
+    <col min="10" max="10" width="42.109375" style="2" customWidth="1"/>
+    <col min="11" max="24" width="13.5546875" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -695,238 +710,233 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>2025</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>2019</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>2020</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>2023</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>2023</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>2023</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>2024</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>